--- a/summary/ZAM/ZAM_export.xlsx
+++ b/summary/ZAM/ZAM_export.xlsx
@@ -2882,13 +2882,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C80A8CA2-BFAF-4FC0-BB7E-3C08ADF3BE43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF040899-033F-4072-97ED-FA89D6B000BD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8750DBC1-112E-4844-9CCF-E43A5F683730}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DA43996-EF55-4353-A142-4631BC1FC211}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97FDD7BC-37D2-40BF-9FD4-8B4B635D6386}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD8C929B-4A6E-46C4-8054-75DE8E131FEB}"/>
 </file>